--- a/Producao/Modelos/REQUISICAO_KIT_MODELO.xlsx
+++ b/Producao/Modelos/REQUISICAO_KIT_MODELO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CIPOLATTI\SISTEMAS\Producao\Producao\Modelos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\Codex\2026-05-21\clona-o-repositorio-wognascimento-financeiro-git\Producao\Producao\Modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D3517B-6587-40E1-BC77-D68265A99795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710BDF2B-6858-4337-8958-0336CEE9A489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{795787B9-A603-4E9F-9555-87E07481D83A}"/>
   </bookViews>
@@ -390,9 +390,39 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -417,68 +447,38 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -808,129 +808,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="27"/>
       <c r="G2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="21"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="23"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="17"/>
       <c r="L2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="21"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="23"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="17"/>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="12" t="s">
+      <c r="A3" s="24"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
       <c r="K3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="L3" s="4"/>
-      <c r="M3" s="27" t="s">
+      <c r="M3" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="28"/>
+      <c r="N3" s="14"/>
       <c r="O3" s="9"/>
       <c r="P3" s="6"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="29" t="s">
+      <c r="B5" s="18"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="30"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="23"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="17"/>
       <c r="N5" s="5"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="29" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="30"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="23"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="17"/>
       <c r="N6" s="5"/>
     </row>
     <row r="7" spans="1:19" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="41"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="40"/>
       <c r="G7" s="10"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
@@ -941,20 +941,20 @@
       <c r="N7" s="11"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="35"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="35"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -963,26 +963,26 @@
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32" t="s">
+      <c r="D9" s="32"/>
+      <c r="E9" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="34"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="33"/>
       <c r="L9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="32" t="s">
+      <c r="M9" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="N9" s="34"/>
+      <c r="N9" s="33"/>
       <c r="O9" s="1" t="s">
         <v>17</v>
       </c>
@@ -1384,7 +1384,7 @@
       <c r="N33" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="lcN38BieSVHqHi6FzFPc52FyLoX+8fG0YDP/x0g0mpKZMkk6gOh6lLxNXoRq6PAWZgHsbvx6gQufVIP0eRYk4A==" saltValue="Mp0woxvSmIq9+eftwCpGPQ==" spinCount="100000" sheet="1" autoFilter="0"/>
+  <sheetProtection autoFilter="0"/>
   <autoFilter ref="A9:S9" xr:uid="{DCC889DE-7B05-4795-BCD8-9882F919D78A}">
     <filterColumn colId="2" showButton="0"/>
     <filterColumn colId="4" showButton="0"/>
@@ -1406,6 +1406,10 @@
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="M2:O2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="I3:J3"/>
@@ -1416,10 +1420,6 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:F3"/>
     <mergeCell ref="C4:F4"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="M2:O2"/>
   </mergeCells>
   <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="78" orientation="landscape" r:id="rId1"/>
@@ -1434,7 +1434,6 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <sheetProtection algorithmName="SHA-512" hashValue="zAGxngdG27lZRaexr2cguOKjhpD6JhzfWo570S1uWFXpgfxziXW/FtNLXBUlULGHLAJiefx3cuYWTmbt2nk97Q==" saltValue="VBiHb9ndeVH/36aOhwDWjw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
